--- a/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
   <si>
     <t>KISB</t>
   </si>
@@ -656,151 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F8" s="3">
         <v>19100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>17700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>16000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>14600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>12400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>10500</v>
-      </c>
-      <c r="J8" s="3">
-        <v>9600</v>
-      </c>
-      <c r="K8" s="3">
-        <v>9600</v>
       </c>
       <c r="L8" s="3">
         <v>9600</v>
       </c>
       <c r="M8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="N8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="O8" s="3">
         <v>10300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>10100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>9400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>10700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9500</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -855,8 +868,14 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -911,8 +930,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +958,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1016,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1078,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,8 +1140,14 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1202,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1227,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F17" s="3">
         <v>8300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>2000</v>
       </c>
       <c r="N17" s="3">
         <v>1800</v>
       </c>
       <c r="O17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q17" s="3">
         <v>2400</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>2800</v>
       </c>
       <c r="R17" s="3">
         <v>2800</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="T17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10800</v>
+        <v>11300</v>
       </c>
       <c r="E18" s="3">
         <v>10700</v>
       </c>
       <c r="F18" s="3">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="G18" s="3">
         <v>10700</v>
       </c>
       <c r="H18" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J18" s="3">
         <v>10200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>9100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>8200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>8100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>7800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>8300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>7500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>6600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>7900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>6700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,64 +1375,72 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-6600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-6900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-6800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-6100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-5800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-5800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-5400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-5200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-5200</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1422,8 +1495,14 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1478,105 +1557,117 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G23" s="3">
         <v>3800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>4600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>4400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>3100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1600</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
+        <v>700</v>
+      </c>
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>500</v>
       </c>
       <c r="O24" s="3">
         <v>400</v>
       </c>
       <c r="P24" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="Q24" s="3">
         <v>400</v>
@@ -1584,14 +1675,20 @@
       <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>400</v>
+      </c>
+      <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1743,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G26" s="3">
         <v>3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>3700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G27" s="3">
         <v>3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2115,138 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F32" s="3">
         <v>6600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>6900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>6800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>6100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>5800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>5800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>5400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>4600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>5200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>5200</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G33" s="3">
         <v>3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2301,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G35" s="3">
         <v>3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,120 +2482,134 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F41" s="3">
         <v>11800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>11100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>10400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>7900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F42" s="3">
         <v>26000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>13600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>12500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>11900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>31100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>21200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>57400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>89400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>69600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>50900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>101900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>117200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>34100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>48000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>43500</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2479,8 +2664,14 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,8 +2726,14 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2591,8 +2788,14 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2647,8 +2850,14 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2703,64 +2912,76 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>27400</v>
+      </c>
+      <c r="F48" s="3">
         <v>27700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>27000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>26900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>26800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>27300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>27000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>26100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>25600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>25000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>25200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>25400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>24300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>21400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>18700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>16700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2807,16 +3028,22 @@
         <v>3600</v>
       </c>
       <c r="R49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="S49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T49" s="3">
         <v>1800</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3160,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2983,8 +3222,14 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3284,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1549600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1542800</v>
+      </c>
+      <c r="F54" s="3">
         <v>1474100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1424100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1374100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1295400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1284700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1219000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1237900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1232800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1196700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1159300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1140400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1106600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1047000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1048400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>953200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3398,72 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>35000</v>
+      </c>
+      <c r="F57" s="3">
         <v>43400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>36500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>33500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>33600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>27700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>13900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>15700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>18400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>20100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>19200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>19500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>24800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>24600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>26900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>24700</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3251,8 +3518,14 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3307,8 +3580,14 @@
       <c r="T59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3363,64 +3642,76 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>41400</v>
+      </c>
+      <c r="F61" s="3">
         <v>43500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>48100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>52100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>52400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>72900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>66800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>58900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>67200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>67800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>69500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>59100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>64700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>68000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>72500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>75300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3475,8 +3766,14 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3952,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1452800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1450000</v>
+      </c>
+      <c r="F66" s="3">
         <v>1389600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1345400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1296900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1223500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1216700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1149200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1165400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1155700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1121000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1085200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1069200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1036600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>979600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>982800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>889500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +4162,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4286,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>98900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>96900</v>
+      </c>
+      <c r="F72" s="3">
         <v>94500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>91900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>89700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>85800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>83000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>80100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>78200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>76400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>74900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>73300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>71500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>69500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>67600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>66500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>65000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4534,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>92800</v>
+      </c>
+      <c r="F76" s="3">
         <v>84500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>78700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>77200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>72000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>68000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>69800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>72400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>77100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>75700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>74100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>71100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>70000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>67300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>65700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>63700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4658,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G81" s="3">
         <v>3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4815,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4476,8 +4873,14 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,8 +5183,14 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4812,8 +5245,14 @@
       <c r="T89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5273,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4890,8 +5331,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,8 +5455,14 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5058,8 +5517,14 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5545,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5603,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,8 +5789,14 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5360,8 +5851,14 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,8 +5913,14 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5470,6 +5973,12 @@
         <v>0</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>KISB</t>
   </si>
@@ -656,164 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>21400</v>
+        <v>15800</v>
       </c>
       <c r="E8" s="3">
-        <v>20600</v>
+        <v>14200</v>
       </c>
       <c r="F8" s="3">
-        <v>19100</v>
+        <v>14200</v>
       </c>
       <c r="G8" s="3">
-        <v>17700</v>
+        <v>13800</v>
       </c>
       <c r="H8" s="3">
-        <v>16000</v>
+        <v>13800</v>
       </c>
       <c r="I8" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K8" s="3">
         <v>14600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>12400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>10500</v>
-      </c>
-      <c r="L8" s="3">
-        <v>9600</v>
-      </c>
-      <c r="M8" s="3">
-        <v>9600</v>
       </c>
       <c r="N8" s="3">
         <v>9600</v>
       </c>
       <c r="O8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="P8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="Q8" s="3">
         <v>10300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>10100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>9900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9500</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -874,31 +887,37 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>14200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>13800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>14000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -936,8 +955,14 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +985,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1049,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,31 +1117,37 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1146,31 +1185,37 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1208,8 +1253,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1280,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E17" s="3">
         <v>10100</v>
       </c>
-      <c r="E17" s="3">
-        <v>9900</v>
-      </c>
       <c r="F17" s="3">
-        <v>8300</v>
+        <v>10300</v>
       </c>
       <c r="G17" s="3">
-        <v>7000</v>
+        <v>9200</v>
       </c>
       <c r="H17" s="3">
-        <v>5300</v>
+        <v>9200</v>
       </c>
       <c r="I17" s="3">
+        <v>9600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K17" s="3">
         <v>3900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="O17" s="3">
-        <v>2000</v>
       </c>
       <c r="P17" s="3">
         <v>1800</v>
       </c>
       <c r="Q17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S17" s="3">
         <v>2400</v>
-      </c>
-      <c r="R17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="S17" s="3">
-        <v>2800</v>
       </c>
       <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="V17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11300</v>
+        <v>5400</v>
       </c>
       <c r="E18" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K18" s="3">
         <v>10700</v>
       </c>
-      <c r="F18" s="3">
-        <v>10800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>10700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>10700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>10700</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>10200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>8200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>8100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>8300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>7500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>6600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>7900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>6700</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,93 +1442,101 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-7600</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>-6500</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>-6600</v>
+        <v>300</v>
       </c>
       <c r="G20" s="3">
-        <v>-6900</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
-        <v>-6800</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-6100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-5800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-5800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-5700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-5100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-5400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-4600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-5200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-5200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>4500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>4700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1501,31 +1574,37 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1563,87 +1642,99 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F23" s="3">
         <v>3700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>4200</v>
       </c>
-      <c r="G23" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>3900</v>
-      </c>
       <c r="I23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K23" s="3">
         <v>4600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>3100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
+        <v>600</v>
+      </c>
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>600</v>
       </c>
       <c r="I24" s="3">
         <v>700</v>
@@ -1652,28 +1743,28 @@
         <v>700</v>
       </c>
       <c r="K24" s="3">
+        <v>700</v>
+      </c>
+      <c r="L24" s="3">
+        <v>700</v>
+      </c>
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>500</v>
       </c>
       <c r="Q24" s="3">
         <v>400</v>
       </c>
       <c r="R24" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="S24" s="3">
         <v>400</v>
@@ -1681,14 +1772,20 @@
       <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>400</v>
+      </c>
+      <c r="V24" s="3">
+        <v>200</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1846,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G26" s="3">
         <v>3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3500</v>
       </c>
-      <c r="G26" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>3300</v>
-      </c>
       <c r="I26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K26" s="3">
         <v>3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G27" s="3">
         <v>3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3500</v>
       </c>
-      <c r="G27" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>3300</v>
-      </c>
       <c r="I27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K27" s="3">
         <v>3800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>2700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +2050,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2118,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2186,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2254,150 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>7600</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>6500</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>6600</v>
+        <v>-300</v>
       </c>
       <c r="G32" s="3">
-        <v>6900</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
-        <v>6800</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>6100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>5800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>5800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>5700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>5100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>5400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>5200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>4600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>5200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>5200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G33" s="3">
         <v>3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3500</v>
       </c>
-      <c r="G33" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H33" s="3">
-        <v>3300</v>
-      </c>
       <c r="I33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K33" s="3">
         <v>3800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>2700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2458,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G35" s="3">
         <v>3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3500</v>
       </c>
-      <c r="G35" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H35" s="3">
-        <v>3300</v>
-      </c>
       <c r="I35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K35" s="3">
         <v>3800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>2700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2629,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,155 +2655,169 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>9800</v>
+        <v>21600</v>
       </c>
       <c r="E41" s="3">
-        <v>13300</v>
+        <v>15300</v>
       </c>
       <c r="F41" s="3">
-        <v>11800</v>
+        <v>18500</v>
       </c>
       <c r="G41" s="3">
-        <v>12900</v>
+        <v>29700</v>
       </c>
       <c r="H41" s="3">
-        <v>10900</v>
+        <v>29700</v>
       </c>
       <c r="I41" s="3">
+        <v>23900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>23900</v>
+      </c>
+      <c r="K41" s="3">
         <v>11100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>12400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>15000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>10400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7900</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>19000</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>26000</v>
+        <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>13600</v>
+        <v>9500</v>
       </c>
       <c r="H42" s="3">
-        <v>12500</v>
+        <v>9500</v>
       </c>
       <c r="I42" s="3">
+        <v>200</v>
+      </c>
+      <c r="J42" s="3">
+        <v>200</v>
+      </c>
+      <c r="K42" s="3">
         <v>11900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>31100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>21200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>57400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>89400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>69600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>50900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>101900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>117200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>34100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>48000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>43500</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2670,31 +2855,37 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2732,31 +2923,37 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>37200</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>32900</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2794,31 +2991,37 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>54100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>54800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>51800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2856,31 +3059,37 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>183100</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>183600</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>185200</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>192600</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>192600</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>193400</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>193400</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2918,70 +3127,82 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E48" s="3">
         <v>27100</v>
       </c>
-      <c r="E48" s="3">
-        <v>27400</v>
-      </c>
       <c r="F48" s="3">
-        <v>27700</v>
+        <v>27100</v>
       </c>
       <c r="G48" s="3">
+        <v>31800</v>
+      </c>
+      <c r="H48" s="3">
+        <v>31800</v>
+      </c>
+      <c r="I48" s="3">
         <v>27000</v>
       </c>
-      <c r="H48" s="3">
-        <v>26900</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K48" s="3">
         <v>26800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>27300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>27000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>26100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>25600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>25000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>25200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>25400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>24300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>21400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>18700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>16700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2995,10 +3216,10 @@
         <v>3600</v>
       </c>
       <c r="G49" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="H49" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="I49" s="3">
         <v>3600</v>
@@ -3034,16 +3255,22 @@
         <v>3600</v>
       </c>
       <c r="T49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="U49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="V49" s="3">
         <v>1800</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3331,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,31 +3399,37 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>33200</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>31700</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>34100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3228,8 +3467,14 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3535,82 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1664800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1611900</v>
+      </c>
+      <c r="F54" s="3">
         <v>1549600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1542800</v>
       </c>
-      <c r="F54" s="3">
-        <v>1474100</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>1542800</v>
+      </c>
+      <c r="I54" s="3">
         <v>1424100</v>
       </c>
-      <c r="H54" s="3">
-        <v>1374100</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
+        <v>1424100</v>
+      </c>
+      <c r="K54" s="3">
         <v>1295400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1284700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1219000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1237900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1232800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1196700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1159300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1140400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1106600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1047000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1048400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>953200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3633,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,70 +3659,78 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>38600</v>
+        <v>1296500</v>
       </c>
       <c r="E57" s="3">
-        <v>35000</v>
+        <v>1270000</v>
       </c>
       <c r="F57" s="3">
-        <v>43400</v>
+        <v>1192100</v>
       </c>
       <c r="G57" s="3">
-        <v>36500</v>
+        <v>1179100</v>
       </c>
       <c r="H57" s="3">
-        <v>33500</v>
+        <v>1179100</v>
       </c>
       <c r="I57" s="3">
+        <v>1091400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1091400</v>
+      </c>
+      <c r="K57" s="3">
         <v>33600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>27700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>13900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>15700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>18400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>20100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>19200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>19500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>24800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>24600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>26900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>24700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3471,22 +3738,22 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>185600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>169400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>169400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3524,31 +3791,37 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -3586,31 +3859,37 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1327100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1477100</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1416300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1402600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1402600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1297300</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1297300</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3648,93 +3927,105 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>233300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>35800</v>
+      </c>
+      <c r="F61" s="3">
         <v>36500</v>
       </c>
-      <c r="E61" s="3">
-        <v>41400</v>
-      </c>
-      <c r="F61" s="3">
-        <v>43500</v>
-      </c>
       <c r="G61" s="3">
+        <v>45400</v>
+      </c>
+      <c r="H61" s="3">
+        <v>45400</v>
+      </c>
+      <c r="I61" s="3">
         <v>48100</v>
       </c>
-      <c r="H61" s="3">
-        <v>52100</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>48100</v>
+      </c>
+      <c r="K61" s="3">
         <v>52400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>72900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>66800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>58900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>67200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>67800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>69500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>59100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>64700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>68000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>72500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>75300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3772,8 +4063,14 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +4131,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4199,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4267,82 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1560500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1512900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1452800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1450000</v>
       </c>
-      <c r="F66" s="3">
-        <v>1389600</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>1450000</v>
+      </c>
+      <c r="I66" s="3">
         <v>1345400</v>
       </c>
-      <c r="H66" s="3">
-        <v>1296900</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
+        <v>1345400</v>
+      </c>
+      <c r="K66" s="3">
         <v>1223500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1216700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1149200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1165400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1155700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1121000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1085200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1069200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1036600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>979600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>982800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>889500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4365,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4429,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4497,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4565,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4633,82 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>100900</v>
+      </c>
+      <c r="F72" s="3">
         <v>98900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>96900</v>
       </c>
-      <c r="F72" s="3">
-        <v>94500</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>96900</v>
+      </c>
+      <c r="I72" s="3">
         <v>91900</v>
       </c>
-      <c r="H72" s="3">
-        <v>89700</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
+        <v>91900</v>
+      </c>
+      <c r="K72" s="3">
         <v>85800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>83000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>80100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>78200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>76400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>74900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>73300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>71500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>69500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>67600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>66500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>65000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4769,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4837,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4905,82 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>104300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F76" s="3">
         <v>96800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>92800</v>
       </c>
-      <c r="F76" s="3">
-        <v>84500</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>92800</v>
+      </c>
+      <c r="I76" s="3">
         <v>78700</v>
       </c>
-      <c r="H76" s="3">
-        <v>77200</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
+        <v>78700</v>
+      </c>
+      <c r="K76" s="3">
         <v>72000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>68000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>69800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>72400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>77100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>75700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>74100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>71100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>70000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>67300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>65700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>63700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +5041,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G81" s="3">
         <v>3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3500</v>
       </c>
-      <c r="G81" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H81" s="3">
-        <v>3300</v>
-      </c>
       <c r="I81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K81" s="3">
         <v>3800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>2700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,31 +5212,33 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4879,8 +5276,14 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5344,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5412,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5480,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5548,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,31 +5616,37 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -5251,8 +5684,14 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,31 +5714,33 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5337,8 +5778,14 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5846,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,31 +5914,37 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -5523,8 +5982,14 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,31 +6012,33 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5609,8 +6076,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +6144,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +6212,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,31 +6280,37 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -5857,31 +6348,37 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5919,31 +6416,37 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -5979,6 +6482,12 @@
         <v>0</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
   <si>
     <t>KISB</t>
   </si>
@@ -656,144 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45107</v>
       </c>
       <c r="J7" s="2">
         <v>45107</v>
       </c>
       <c r="K7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E8" s="3">
         <v>15800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>14200</v>
       </c>
       <c r="F8" s="3">
         <v>14200</v>
       </c>
       <c r="G8" s="3">
-        <v>13800</v>
+        <v>14200</v>
       </c>
       <c r="H8" s="3">
-        <v>13800</v>
+        <v>13600</v>
       </c>
       <c r="I8" s="3">
         <v>14000</v>
       </c>
       <c r="J8" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K8" s="3">
         <v>14000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10500</v>
-      </c>
-      <c r="N8" s="3">
-        <v>9600</v>
       </c>
       <c r="O8" s="3">
         <v>9600</v>
@@ -802,31 +805,34 @@
         <v>9600</v>
       </c>
       <c r="Q8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="R8" s="3">
         <v>10300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9500</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -893,35 +899,38 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E10" s="3">
         <v>15800</v>
-      </c>
-      <c r="E10" s="3">
-        <v>14200</v>
       </c>
       <c r="F10" s="3">
         <v>14200</v>
       </c>
       <c r="G10" s="3">
-        <v>13800</v>
+        <v>14200</v>
       </c>
       <c r="H10" s="3">
-        <v>13800</v>
+        <v>13600</v>
       </c>
       <c r="I10" s="3">
         <v>14000</v>
       </c>
       <c r="J10" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K10" s="3">
         <v>14000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,8 +999,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1055,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,8 +1139,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1149,8 +1168,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1191,8 +1210,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1209,7 +1231,7 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>400</v>
@@ -1218,7 +1240,7 @@
         <v>400</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1259,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,61 +1307,62 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E17" s="3">
         <v>10400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10300</v>
       </c>
-      <c r="G17" s="3">
-        <v>9200</v>
-      </c>
       <c r="H17" s="3">
-        <v>9200</v>
+        <v>8900</v>
       </c>
       <c r="I17" s="3">
         <v>9600</v>
       </c>
       <c r="J17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="K17" s="3">
         <v>9600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1400</v>
       </c>
       <c r="N17" s="3">
         <v>1400</v>
       </c>
       <c r="O17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2400</v>
-      </c>
-      <c r="T17" s="3">
-        <v>2800</v>
       </c>
       <c r="U17" s="3">
         <v>2800</v>
@@ -1344,82 +1370,88 @@
       <c r="V17" s="3">
         <v>2800</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>2800</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E18" s="3">
         <v>5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4000</v>
       </c>
-      <c r="G18" s="3">
-        <v>4600</v>
-      </c>
       <c r="H18" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="I18" s="3">
         <v>4400</v>
       </c>
       <c r="J18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K18" s="3">
         <v>4400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7800</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>8300</v>
       </c>
       <c r="R18" s="3">
         <v>8300</v>
       </c>
       <c r="S18" s="3">
+        <v>8300</v>
+      </c>
+      <c r="T18" s="3">
         <v>7500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6700</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,8 +1476,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1459,10 +1492,10 @@
         <v>300</v>
       </c>
       <c r="G20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H20" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I20" s="3">
         <v>200</v>
@@ -1471,76 +1504,79 @@
         <v>200</v>
       </c>
       <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-5800</v>
       </c>
       <c r="M20" s="3">
         <v>-5800</v>
       </c>
       <c r="N20" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="O20" s="3">
         <v>-5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4600</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-5200</v>
       </c>
       <c r="V20" s="3">
         <v>-5200</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>-5200</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E21" s="3">
         <v>5400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K21" s="3">
         <v>4700</v>
       </c>
-      <c r="J21" s="3">
-        <v>4700</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1616,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1606,8 +1645,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1648,22 +1687,25 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>4200</v>
       </c>
       <c r="H23" s="3">
         <v>4200</v>
@@ -1672,52 +1714,55 @@
         <v>4200</v>
       </c>
       <c r="J23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K23" s="3">
         <v>4200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3000</v>
-      </c>
-      <c r="R23" s="3">
-        <v>3100</v>
       </c>
       <c r="S23" s="3">
         <v>3100</v>
       </c>
       <c r="T23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="U23" s="3">
         <v>2000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1600</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1725,13 +1770,13 @@
         <v>900</v>
       </c>
       <c r="E24" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F24" s="3">
         <v>600</v>
       </c>
       <c r="G24" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H24" s="3">
         <v>700</v>
@@ -1740,7 +1785,7 @@
         <v>700</v>
       </c>
       <c r="J24" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K24" s="3">
         <v>700</v>
@@ -1749,43 +1794,46 @@
         <v>700</v>
       </c>
       <c r="M24" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N24" s="3">
         <v>500</v>
       </c>
       <c r="O24" s="3">
+        <v>500</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,22 +1900,25 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>4200</v>
-      </c>
-      <c r="E26" s="3">
-        <v>3100</v>
       </c>
       <c r="F26" s="3">
         <v>3100</v>
       </c>
       <c r="G26" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="H26" s="3">
         <v>3500</v>
@@ -1876,66 +1927,69 @@
         <v>3500</v>
       </c>
       <c r="J26" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K26" s="3">
         <v>3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2600</v>
-      </c>
-      <c r="O26" s="3">
-        <v>2300</v>
       </c>
       <c r="P26" s="3">
         <v>2300</v>
       </c>
       <c r="Q26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R26" s="3">
         <v>2600</v>
-      </c>
-      <c r="R26" s="3">
-        <v>2700</v>
       </c>
       <c r="S26" s="3">
         <v>2700</v>
       </c>
       <c r="T26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U26" s="3">
         <v>1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E27" s="3">
         <v>4200</v>
-      </c>
-      <c r="E27" s="3">
-        <v>3100</v>
       </c>
       <c r="F27" s="3">
         <v>3100</v>
       </c>
       <c r="G27" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="H27" s="3">
         <v>3500</v>
@@ -1944,52 +1998,55 @@
         <v>3500</v>
       </c>
       <c r="J27" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K27" s="3">
         <v>3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>2300</v>
       </c>
       <c r="P27" s="3">
         <v>2300</v>
       </c>
       <c r="Q27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R27" s="3">
         <v>2600</v>
-      </c>
-      <c r="R27" s="3">
-        <v>2700</v>
       </c>
       <c r="S27" s="3">
         <v>2700</v>
       </c>
       <c r="T27" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U27" s="3">
         <v>1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,8 +2326,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2275,10 +2344,10 @@
         <v>-300</v>
       </c>
       <c r="G32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="H32" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="I32" s="3">
         <v>-200</v>
@@ -2287,63 +2356,66 @@
         <v>-200</v>
       </c>
       <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
         <v>6100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>5800</v>
       </c>
       <c r="M32" s="3">
         <v>5800</v>
       </c>
       <c r="N32" s="3">
+        <v>5800</v>
+      </c>
+      <c r="O32" s="3">
         <v>5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4600</v>
-      </c>
-      <c r="U32" s="3">
-        <v>5200</v>
       </c>
       <c r="V32" s="3">
         <v>5200</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>5200</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E33" s="3">
         <v>4200</v>
-      </c>
-      <c r="E33" s="3">
-        <v>3100</v>
       </c>
       <c r="F33" s="3">
         <v>3100</v>
       </c>
       <c r="G33" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="H33" s="3">
         <v>3500</v>
@@ -2352,52 +2424,55 @@
         <v>3500</v>
       </c>
       <c r="J33" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K33" s="3">
         <v>3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>2300</v>
       </c>
       <c r="P33" s="3">
         <v>2300</v>
       </c>
       <c r="Q33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R33" s="3">
         <v>2600</v>
-      </c>
-      <c r="R33" s="3">
-        <v>2700</v>
       </c>
       <c r="S33" s="3">
         <v>2700</v>
       </c>
       <c r="T33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U33" s="3">
         <v>1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,22 +2539,25 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E35" s="3">
         <v>4200</v>
-      </c>
-      <c r="E35" s="3">
-        <v>3100</v>
       </c>
       <c r="F35" s="3">
         <v>3100</v>
       </c>
       <c r="G35" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="H35" s="3">
         <v>3500</v>
@@ -2488,125 +2566,131 @@
         <v>3500</v>
       </c>
       <c r="J35" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K35" s="3">
         <v>3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>2300</v>
       </c>
       <c r="P35" s="3">
         <v>2300</v>
       </c>
       <c r="Q35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R35" s="3">
         <v>2600</v>
-      </c>
-      <c r="R35" s="3">
-        <v>2700</v>
       </c>
       <c r="S35" s="3">
         <v>2700</v>
       </c>
       <c r="T35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U35" s="3">
         <v>1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45107</v>
       </c>
       <c r="J38" s="2">
         <v>45107</v>
       </c>
       <c r="K38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,76 +2742,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E41" s="3">
         <v>21600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18500</v>
-      </c>
-      <c r="G41" s="3">
-        <v>29700</v>
       </c>
       <c r="H41" s="3">
         <v>29700</v>
       </c>
-      <c r="I41" s="3">
-        <v>23900</v>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J41" s="3">
         <v>23900</v>
       </c>
       <c r="K41" s="3">
+        <v>23900</v>
+      </c>
+      <c r="L41" s="3">
         <v>11100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7900</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2734,67 +2823,70 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>9500</v>
+        <v>200</v>
       </c>
       <c r="H42" s="3">
         <v>9500</v>
       </c>
       <c r="I42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>200</v>
       </c>
       <c r="K42" s="3">
+        <v>200</v>
+      </c>
+      <c r="L42" s="3">
         <v>11900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>31100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>21200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>57400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>89400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>69600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>50900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>101900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>117200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>34100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>48000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>43500</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2819,8 +2911,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2861,8 +2953,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2887,8 +2982,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2929,34 +3024,37 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E45" s="3">
         <v>30000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1100</v>
       </c>
       <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
-        <v>32700</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
         <v>32700</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2997,34 +3095,37 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E46" s="3">
         <v>54100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>54800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>51800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>41000</v>
       </c>
       <c r="H46" s="3">
         <v>41000</v>
       </c>
-      <c r="I46" s="3">
-        <v>58500</v>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J46" s="3">
         <v>58500</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -3065,34 +3166,37 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>163100</v>
+      </c>
+      <c r="E47" s="3">
         <v>183100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>183600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>185200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>192600</v>
       </c>
       <c r="H47" s="3">
         <v>192600</v>
       </c>
-      <c r="I47" s="3">
-        <v>193400</v>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
         <v>193400</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>193400</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3133,81 +3237,87 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E48" s="3">
         <v>27600</v>
-      </c>
-      <c r="E48" s="3">
-        <v>27100</v>
       </c>
       <c r="F48" s="3">
         <v>27100</v>
       </c>
       <c r="G48" s="3">
-        <v>31800</v>
+        <v>27100</v>
       </c>
       <c r="H48" s="3">
         <v>31800</v>
       </c>
-      <c r="I48" s="3">
-        <v>27000</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J48" s="3">
         <v>27000</v>
       </c>
       <c r="K48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="L48" s="3">
         <v>26800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>27300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16700</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="E49" s="3">
         <v>3600</v>
@@ -3216,13 +3326,13 @@
         <v>3600</v>
       </c>
       <c r="G49" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="H49" s="3">
         <v>3700</v>
       </c>
       <c r="I49" s="3">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>3600</v>
@@ -3261,16 +3371,19 @@
         <v>3600</v>
       </c>
       <c r="V49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W49" s="3">
         <v>1800</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,34 +3521,37 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E52" s="3">
         <v>33200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>48400</v>
       </c>
       <c r="H52" s="3">
         <v>48400</v>
       </c>
-      <c r="I52" s="3">
-        <v>33300</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
         <v>33300</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3473,8 +3592,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,76 +3663,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1692600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1664800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1611900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1549600</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1542800</v>
       </c>
       <c r="H54" s="3">
         <v>1542800</v>
       </c>
-      <c r="I54" s="3">
-        <v>1424100</v>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J54" s="3">
         <v>1424100</v>
       </c>
       <c r="K54" s="3">
+        <v>1424100</v>
+      </c>
+      <c r="L54" s="3">
         <v>1295400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1284700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1219000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1237900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1232800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1196700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1159300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1140400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1106600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1047000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1048400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>953200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,76 +3790,80 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1298100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1296500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1270000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1192100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1179100</v>
       </c>
       <c r="H57" s="3">
         <v>1179100</v>
       </c>
-      <c r="I57" s="3">
-        <v>1091400</v>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J57" s="3">
         <v>1091400</v>
       </c>
       <c r="K57" s="3">
+        <v>1091400</v>
+      </c>
+      <c r="L57" s="3">
         <v>33600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>24800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>26900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>24700</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3738,25 +3871,25 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>168000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>185600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>200600</v>
       </c>
       <c r="H58" s="3">
         <v>200600</v>
       </c>
       <c r="I58" s="3">
-        <v>169400</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>169400</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>169400</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3797,8 +3930,11 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3823,8 +3959,8 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -3865,34 +4001,37 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1333800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1327100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1477100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1416300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1402600</v>
       </c>
       <c r="H60" s="3">
         <v>1402600</v>
       </c>
-      <c r="I60" s="3">
-        <v>1297300</v>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J60" s="3">
         <v>1297300</v>
       </c>
       <c r="K60" s="3">
-        <v>0</v>
+        <v>1297300</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -3933,76 +4072,82 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>252600</v>
+      </c>
+      <c r="E61" s="3">
         <v>233300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36500</v>
-      </c>
-      <c r="G61" s="3">
-        <v>45400</v>
       </c>
       <c r="H61" s="3">
         <v>45400</v>
       </c>
       <c r="I61" s="3">
-        <v>48100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>48100</v>
       </c>
       <c r="K61" s="3">
+        <v>48100</v>
+      </c>
+      <c r="L61" s="3">
         <v>52400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>72900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>66800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>58900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>67200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>67800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>69500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>59100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>64700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>68000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>72500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>75300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4015,8 +4160,8 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
-        <v>2000</v>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>2000</v>
@@ -4027,8 +4172,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4069,8 +4214,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,76 +4427,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1586400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1560500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1512900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1452800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1450000</v>
       </c>
       <c r="H66" s="3">
         <v>1450000</v>
       </c>
-      <c r="I66" s="3">
-        <v>1345400</v>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J66" s="3">
         <v>1345400</v>
       </c>
       <c r="K66" s="3">
+        <v>1345400</v>
+      </c>
+      <c r="L66" s="3">
         <v>1223500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1216700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1149200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1165400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1155700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1121000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1085200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1069200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1036600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>979600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>982800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>889500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,76 +4809,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E72" s="3">
         <v>104000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>100900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>98900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>96900</v>
       </c>
       <c r="H72" s="3">
         <v>96900</v>
       </c>
-      <c r="I72" s="3">
-        <v>91900</v>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J72" s="3">
         <v>91900</v>
       </c>
       <c r="K72" s="3">
+        <v>91900</v>
+      </c>
+      <c r="L72" s="3">
         <v>85800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>83000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>80100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>78200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>76400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>74900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>73300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>71500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>69500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>67600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>66500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>65000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,76 +5093,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E76" s="3">
         <v>104300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>99000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>96800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>92800</v>
       </c>
       <c r="H76" s="3">
         <v>92800</v>
       </c>
-      <c r="I76" s="3">
-        <v>78700</v>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J76" s="3">
         <v>78700</v>
       </c>
       <c r="K76" s="3">
+        <v>78700</v>
+      </c>
+      <c r="L76" s="3">
         <v>72000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>68000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>69800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>72400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>77100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>74100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>71100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>70000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>67300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>65700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>63700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,95 +5235,101 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45107</v>
       </c>
       <c r="J80" s="2">
         <v>45107</v>
       </c>
       <c r="K80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E81" s="3">
         <v>4200</v>
-      </c>
-      <c r="E81" s="3">
-        <v>3100</v>
       </c>
       <c r="F81" s="3">
         <v>3100</v>
       </c>
       <c r="G81" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="H81" s="3">
         <v>3500</v>
@@ -5144,52 +5338,55 @@
         <v>3500</v>
       </c>
       <c r="J81" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K81" s="3">
         <v>3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>2300</v>
       </c>
       <c r="P81" s="3">
         <v>2300</v>
       </c>
       <c r="Q81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R81" s="3">
         <v>2600</v>
-      </c>
-      <c r="R81" s="3">
-        <v>2700</v>
       </c>
       <c r="S81" s="3">
         <v>2700</v>
       </c>
       <c r="T81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U81" s="3">
         <v>1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5411,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5240,8 +5438,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -5282,8 +5480,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,8 +5835,11 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5648,8 +5864,8 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -5690,8 +5906,11 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,8 +5935,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5742,8 +5962,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5784,8 +6004,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,8 +6146,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5946,8 +6175,8 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -5988,8 +6217,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6040,8 +6273,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6082,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,8 +6528,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6312,8 +6557,8 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -6354,8 +6599,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6380,8 +6628,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6422,8 +6670,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6448,8 +6699,8 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -6488,6 +6739,9 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>KISB</t>
   </si>
@@ -656,150 +656,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45107</v>
       </c>
       <c r="K7" s="2">
         <v>45107</v>
       </c>
       <c r="L7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>14200</v>
       </c>
       <c r="G8" s="3">
         <v>14200</v>
       </c>
       <c r="H8" s="3">
+        <v>14200</v>
+      </c>
+      <c r="I8" s="3">
         <v>13600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10500</v>
-      </c>
-      <c r="O8" s="3">
-        <v>9600</v>
       </c>
       <c r="P8" s="3">
         <v>9600</v>
@@ -808,31 +812,34 @@
         <v>9600</v>
       </c>
       <c r="R8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="S8" s="3">
         <v>10300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9500</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,38 +909,41 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E10" s="3">
         <v>16200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15800</v>
-      </c>
-      <c r="F10" s="3">
-        <v>14200</v>
       </c>
       <c r="G10" s="3">
         <v>14200</v>
       </c>
       <c r="H10" s="3">
+        <v>14200</v>
+      </c>
+      <c r="I10" s="3">
         <v>13600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,8 +1013,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,8 +1159,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1171,8 +1191,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1213,16 +1233,19 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
@@ -1234,7 +1257,7 @@
         <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>400</v>
@@ -1243,7 +1266,7 @@
         <v>400</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,64 +1334,65 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E17" s="3">
         <v>10900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1400</v>
       </c>
       <c r="O17" s="3">
         <v>1400</v>
       </c>
       <c r="P17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2400</v>
-      </c>
-      <c r="U17" s="3">
-        <v>2800</v>
       </c>
       <c r="V17" s="3">
         <v>2800</v>
@@ -1373,85 +1400,91 @@
       <c r="W17" s="3">
         <v>2800</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+      <c r="X17" s="3">
+        <v>2800</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E18" s="3">
         <v>5300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7800</v>
-      </c>
-      <c r="R18" s="3">
-        <v>8300</v>
       </c>
       <c r="S18" s="3">
         <v>8300</v>
       </c>
       <c r="T18" s="3">
+        <v>8300</v>
+      </c>
+      <c r="U18" s="3">
         <v>7500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6700</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,13 +1510,14 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
@@ -1495,10 +1529,10 @@
         <v>300</v>
       </c>
       <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
         <v>500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
@@ -1507,79 +1541,82 @@
         <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-6100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-5800</v>
       </c>
       <c r="N20" s="3">
         <v>-5800</v>
       </c>
       <c r="O20" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="P20" s="3">
         <v>-5200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4600</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-5200</v>
       </c>
       <c r="W20" s="3">
         <v>-5200</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>-5200</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5300</v>
+        <v>4900</v>
       </c>
       <c r="E21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F21" s="3">
         <v>5400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1656,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1648,8 +1688,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1690,105 +1730,111 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E23" s="3">
         <v>5000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3700</v>
-      </c>
-      <c r="H23" s="3">
-        <v>4200</v>
       </c>
       <c r="I23" s="3">
         <v>4200</v>
       </c>
       <c r="J23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K23" s="3">
         <v>3800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3000</v>
-      </c>
-      <c r="S23" s="3">
-        <v>3100</v>
       </c>
       <c r="T23" s="3">
         <v>3100</v>
       </c>
       <c r="U23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="V23" s="3">
         <v>2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1600</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E24" s="3">
         <v>900</v>
       </c>
       <c r="F24" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="G24" s="3">
         <v>600</v>
       </c>
       <c r="H24" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I24" s="3">
         <v>700</v>
       </c>
       <c r="J24" s="3">
+        <v>700</v>
+      </c>
+      <c r="K24" s="3">
         <v>600</v>
-      </c>
-      <c r="K24" s="3">
-        <v>700</v>
       </c>
       <c r="L24" s="3">
         <v>700</v>
@@ -1797,43 +1843,46 @@
         <v>700</v>
       </c>
       <c r="N24" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="O24" s="3">
         <v>500</v>
       </c>
       <c r="P24" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E26" s="3">
         <v>4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>3100</v>
       </c>
       <c r="G26" s="3">
         <v>3100</v>
       </c>
       <c r="H26" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="I26" s="3">
         <v>3500</v>
       </c>
       <c r="J26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K26" s="3">
         <v>3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2600</v>
-      </c>
-      <c r="P26" s="3">
-        <v>2300</v>
       </c>
       <c r="Q26" s="3">
         <v>2300</v>
       </c>
       <c r="R26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S26" s="3">
         <v>2600</v>
-      </c>
-      <c r="S26" s="3">
-        <v>2700</v>
       </c>
       <c r="T26" s="3">
         <v>2700</v>
       </c>
       <c r="U26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V26" s="3">
         <v>1700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E27" s="3">
         <v>4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4200</v>
-      </c>
-      <c r="F27" s="3">
-        <v>3100</v>
       </c>
       <c r="G27" s="3">
         <v>3100</v>
       </c>
       <c r="H27" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="I27" s="3">
         <v>3500</v>
       </c>
       <c r="J27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K27" s="3">
         <v>3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2600</v>
-      </c>
-      <c r="P27" s="3">
-        <v>2300</v>
       </c>
       <c r="Q27" s="3">
         <v>2300</v>
       </c>
       <c r="R27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S27" s="3">
         <v>2600</v>
-      </c>
-      <c r="S27" s="3">
-        <v>2700</v>
       </c>
       <c r="T27" s="3">
         <v>2700</v>
       </c>
       <c r="U27" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V27" s="3">
         <v>1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,13 +2396,16 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
         <v>-300</v>
@@ -2347,10 +2417,10 @@
         <v>-300</v>
       </c>
       <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
@@ -2359,120 +2429,126 @@
         <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
         <v>6100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>5800</v>
       </c>
       <c r="N32" s="3">
         <v>5800</v>
       </c>
       <c r="O32" s="3">
+        <v>5800</v>
+      </c>
+      <c r="P32" s="3">
         <v>5200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4600</v>
-      </c>
-      <c r="V32" s="3">
-        <v>5200</v>
       </c>
       <c r="W32" s="3">
         <v>5200</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>5200</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E33" s="3">
         <v>4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4200</v>
-      </c>
-      <c r="F33" s="3">
-        <v>3100</v>
       </c>
       <c r="G33" s="3">
         <v>3100</v>
       </c>
       <c r="H33" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="I33" s="3">
         <v>3500</v>
       </c>
       <c r="J33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K33" s="3">
         <v>3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2600</v>
-      </c>
-      <c r="P33" s="3">
-        <v>2300</v>
       </c>
       <c r="Q33" s="3">
         <v>2300</v>
       </c>
       <c r="R33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S33" s="3">
         <v>2600</v>
-      </c>
-      <c r="S33" s="3">
-        <v>2700</v>
       </c>
       <c r="T33" s="3">
         <v>2700</v>
       </c>
       <c r="U33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V33" s="3">
         <v>1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E35" s="3">
         <v>4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4200</v>
-      </c>
-      <c r="F35" s="3">
-        <v>3100</v>
       </c>
       <c r="G35" s="3">
         <v>3100</v>
       </c>
       <c r="H35" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="I35" s="3">
         <v>3500</v>
       </c>
       <c r="J35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K35" s="3">
         <v>3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2600</v>
-      </c>
-      <c r="P35" s="3">
-        <v>2300</v>
       </c>
       <c r="Q35" s="3">
         <v>2300</v>
       </c>
       <c r="R35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S35" s="3">
         <v>2600</v>
-      </c>
-      <c r="S35" s="3">
-        <v>2700</v>
       </c>
       <c r="T35" s="3">
         <v>2700</v>
       </c>
       <c r="U35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V35" s="3">
         <v>1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45107</v>
       </c>
       <c r="K38" s="2">
         <v>45107</v>
       </c>
       <c r="L38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,79 +2829,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E41" s="3">
         <v>17200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29700</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
-        <v>23900</v>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>23900</v>
       </c>
       <c r="L41" s="3">
+        <v>23900</v>
+      </c>
+      <c r="M41" s="3">
         <v>11100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7900</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2823,70 +2913,73 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="F42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>200</v>
       </c>
       <c r="H42" s="3">
+        <v>200</v>
+      </c>
+      <c r="I42" s="3">
         <v>9500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>200</v>
       </c>
       <c r="L42" s="3">
+        <v>200</v>
+      </c>
+      <c r="M42" s="3">
         <v>11900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>31100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>21200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>57400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>89400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>69600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>50900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>101900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>117200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>34100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>48000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>43500</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2914,8 +3007,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2985,8 +3081,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3027,37 +3123,40 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>31900</v>
+        <v>32300</v>
       </c>
       <c r="E45" s="3">
+        <v>800</v>
+      </c>
+      <c r="F45" s="3">
         <v>30000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
-        <v>32700</v>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>32700</v>
       </c>
       <c r="L45" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -3098,37 +3197,40 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>49900</v>
+        <v>53000</v>
       </c>
       <c r="E46" s="3">
+        <v>27900</v>
+      </c>
+      <c r="F46" s="3">
         <v>54100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>51800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>41000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3">
-        <v>58500</v>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>58500</v>
       </c>
       <c r="L46" s="3">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -3169,37 +3271,40 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>164300</v>
+      </c>
+      <c r="E47" s="3">
         <v>163100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>183100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>183600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>185200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>192600</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
-        <v>193400</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>193400</v>
       </c>
       <c r="L47" s="3">
-        <v>0</v>
+        <v>193400</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3240,79 +3345,85 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E48" s="3">
         <v>27500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27600</v>
-      </c>
-      <c r="F48" s="3">
-        <v>27100</v>
       </c>
       <c r="G48" s="3">
         <v>27100</v>
       </c>
       <c r="H48" s="3">
-        <v>31800</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
-        <v>27000</v>
+        <v>27100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>27400</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>27000</v>
       </c>
       <c r="L48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="M48" s="3">
         <v>26800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3320,7 +3431,7 @@
         <v>3500</v>
       </c>
       <c r="E49" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="F49" s="3">
         <v>3600</v>
@@ -3329,13 +3440,13 @@
         <v>3600</v>
       </c>
       <c r="H49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I49" s="3">
         <v>3700</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>3600</v>
@@ -3374,16 +3485,19 @@
         <v>3600</v>
       </c>
       <c r="W49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="X49" s="3">
         <v>1800</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,37 +3641,40 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>33400</v>
+        <v>36600</v>
       </c>
       <c r="E52" s="3">
+        <v>55200</v>
+      </c>
+      <c r="F52" s="3">
         <v>33200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>31700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34100</v>
       </c>
-      <c r="H52" s="3">
-        <v>48400</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
-        <v>33300</v>
+      <c r="I52" s="3">
+        <v>52700</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>33300</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,79 +3789,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1692600</v>
+        <v>1771300</v>
       </c>
       <c r="E54" s="3">
+        <v>1692500</v>
+      </c>
+      <c r="F54" s="3">
         <v>1664800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1611900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1549600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1542800</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3">
-        <v>1424100</v>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>1424100</v>
       </c>
       <c r="L54" s="3">
+        <v>1424100</v>
+      </c>
+      <c r="M54" s="3">
         <v>1295400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1284700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1219000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1237900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1232800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1196700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1159300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1140400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1106600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1047000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1048400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>953200</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,79 +3921,83 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1296200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1298100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1296500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1270000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1192100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1179100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1091400</v>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>1091400</v>
       </c>
       <c r="L57" s="3">
+        <v>1091400</v>
+      </c>
+      <c r="M57" s="3">
         <v>33600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>26900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>24700</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3871,28 +4005,28 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>209900</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>168000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>185600</v>
       </c>
-      <c r="H58" s="3">
-        <v>200600</v>
-      </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>194500</v>
       </c>
       <c r="J58" s="3">
-        <v>169400</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>169400</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>169400</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3933,8 +4067,11 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3962,8 +4099,8 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -4004,37 +4141,40 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1333800</v>
+        <v>1329500</v>
       </c>
       <c r="E60" s="3">
+        <v>1530200</v>
+      </c>
+      <c r="F60" s="3">
         <v>1327100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1477100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1416300</v>
       </c>
-      <c r="H60" s="3">
-        <v>1402600</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1297300</v>
+      <c r="I60" s="3">
+        <v>1401000</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>1297300</v>
       </c>
       <c r="L60" s="3">
-        <v>0</v>
+        <v>1297300</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -4075,87 +4215,93 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>252600</v>
+        <v>331800</v>
       </c>
       <c r="E61" s="3">
+        <v>53700</v>
+      </c>
+      <c r="F61" s="3">
         <v>233300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36500</v>
       </c>
-      <c r="H61" s="3">
-        <v>45400</v>
-      </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="J61" s="3">
-        <v>48100</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>48100</v>
       </c>
       <c r="L61" s="3">
+        <v>48100</v>
+      </c>
+      <c r="M61" s="3">
         <v>52400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>72900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>66800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>58900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>67200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>67800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>69500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>59100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>64700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>68000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>72500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>75300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+      <c r="E62" s="3">
+        <v>2500</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -4163,20 +4309,20 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,79 +4585,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1661300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1586400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1560500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1512900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1452800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1450000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1345400</v>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>1345400</v>
       </c>
       <c r="L66" s="3">
+        <v>1345400</v>
+      </c>
+      <c r="M66" s="3">
         <v>1223500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1216700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1149200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1165400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1155700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1121000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1085200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1069200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1036600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>979600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>982800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>889500</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,79 +4983,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E72" s="3">
         <v>107000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>104000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>100900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>98900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>96900</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3">
-        <v>91900</v>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>91900</v>
       </c>
       <c r="L72" s="3">
+        <v>91900</v>
+      </c>
+      <c r="M72" s="3">
         <v>85800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>83000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>80100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>78200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>76400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>74900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>73300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>71500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>69500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>67600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>66500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>65000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,79 +5279,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E76" s="3">
         <v>106100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>104300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>99000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>96800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>92800</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3">
-        <v>78700</v>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>78700</v>
       </c>
       <c r="L76" s="3">
+        <v>78700</v>
+      </c>
+      <c r="M76" s="3">
         <v>72000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>68000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>69800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>72400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>77100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>75700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>74100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>71100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>70000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>67300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>65700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>63700</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45107</v>
       </c>
       <c r="K80" s="2">
         <v>45107</v>
       </c>
       <c r="L80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E81" s="3">
         <v>4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4200</v>
-      </c>
-      <c r="F81" s="3">
-        <v>3100</v>
       </c>
       <c r="G81" s="3">
         <v>3100</v>
       </c>
       <c r="H81" s="3">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="I81" s="3">
         <v>3500</v>
       </c>
       <c r="J81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K81" s="3">
         <v>3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2600</v>
-      </c>
-      <c r="P81" s="3">
-        <v>2300</v>
       </c>
       <c r="Q81" s="3">
         <v>2300</v>
       </c>
       <c r="R81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S81" s="3">
         <v>2600</v>
-      </c>
-      <c r="S81" s="3">
-        <v>2700</v>
       </c>
       <c r="T81" s="3">
         <v>2700</v>
       </c>
       <c r="U81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V81" s="3">
         <v>1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5441,8 +5640,8 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,8 +6052,11 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5867,8 +6084,8 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,8 +6156,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5965,8 +6186,8 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,8 +6376,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6178,8 +6408,8 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6276,8 +6510,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,8 +6774,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6560,8 +6806,8 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -6602,8 +6848,11 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6631,8 +6880,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6673,8 +6922,11 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6702,8 +6954,8 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -6742,6 +6994,9 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KISB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="92">
   <si>
     <t>KISB</t>
   </si>
@@ -656,157 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45107</v>
       </c>
       <c r="L7" s="2">
         <v>45107</v>
       </c>
       <c r="M7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>16000</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>16200</v>
       </c>
-      <c r="F8" s="3">
-        <v>15800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>14200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>14200</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>13600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10500</v>
-      </c>
-      <c r="P8" s="3">
-        <v>9600</v>
       </c>
       <c r="Q8" s="3">
         <v>9600</v>
@@ -815,31 +819,34 @@
         <v>9600</v>
       </c>
       <c r="S8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="T8" s="3">
         <v>10300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9500</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -912,41 +919,44 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>16000</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>16200</v>
       </c>
-      <c r="F10" s="3">
-        <v>15800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>14200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>14200</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>13600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -986,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,8 +1027,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1088,8 +1102,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,8 +1179,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1194,8 +1214,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1236,31 +1256,34 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>600</v>
       </c>
-      <c r="E15" s="3">
-        <v>600</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>400</v>
@@ -1269,7 +1292,7 @@
         <v>400</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,67 +1361,68 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>11200</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
         <v>10900</v>
       </c>
-      <c r="F17" s="3">
-        <v>10400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>10100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>10300</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
         <v>8900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1400</v>
       </c>
       <c r="P17" s="3">
         <v>1400</v>
       </c>
       <c r="Q17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2400</v>
-      </c>
-      <c r="V17" s="3">
-        <v>2800</v>
       </c>
       <c r="W17" s="3">
         <v>2800</v>
@@ -1403,88 +1430,94 @@
       <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
+      <c r="Y17" s="3">
+        <v>2800</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>5300</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>4700</v>
       </c>
-      <c r="E18" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L18" s="3">
         <v>4000</v>
       </c>
-      <c r="I18" s="3">
-        <v>4700</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>4400</v>
       </c>
-      <c r="K18" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>4400</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>8300</v>
       </c>
       <c r="T18" s="3">
         <v>8300</v>
       </c>
       <c r="U18" s="3">
+        <v>8300</v>
+      </c>
+      <c r="V18" s="3">
         <v>7500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,31 +1544,32 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>300</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>300</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
@@ -1544,82 +1578,85 @@
         <v>200</v>
       </c>
       <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
         <v>-6100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-5800</v>
       </c>
       <c r="O20" s="3">
         <v>-5800</v>
       </c>
       <c r="P20" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4600</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-5200</v>
       </c>
       <c r="X20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>-5200</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4900</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>5600</v>
       </c>
-      <c r="F21" s="3">
-        <v>5400</v>
-      </c>
       <c r="G21" s="3">
-        <v>4100</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>4500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,8 +1696,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1691,8 +1731,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1733,111 +1773,117 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>4400</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>5000</v>
       </c>
-      <c r="F23" s="3">
-        <v>5100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H23" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>4200</v>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J23" s="3">
         <v>4200</v>
       </c>
       <c r="K23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L23" s="3">
         <v>3800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>3100</v>
       </c>
       <c r="U23" s="3">
         <v>3100</v>
       </c>
       <c r="V23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="W23" s="3">
         <v>2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1600</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>800</v>
-      </c>
-      <c r="E24" s="3">
-        <v>900</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
-        <v>600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>700</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3">
         <v>700</v>
       </c>
       <c r="K24" s="3">
+        <v>700</v>
+      </c>
+      <c r="L24" s="3">
         <v>600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>700</v>
       </c>
       <c r="M24" s="3">
         <v>700</v>
@@ -1846,43 +1892,46 @@
         <v>700</v>
       </c>
       <c r="O24" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="P24" s="3">
         <v>500</v>
       </c>
       <c r="Q24" s="3">
+        <v>500</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>4100</v>
       </c>
-      <c r="F26" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>3500</v>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J26" s="3">
         <v>3500</v>
       </c>
       <c r="K26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L26" s="3">
         <v>3200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>2300</v>
       </c>
       <c r="R26" s="3">
         <v>2300</v>
       </c>
       <c r="S26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T26" s="3">
         <v>2600</v>
-      </c>
-      <c r="T26" s="3">
-        <v>2700</v>
       </c>
       <c r="U26" s="3">
         <v>2700</v>
       </c>
       <c r="V26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W26" s="3">
         <v>1700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>4100</v>
       </c>
-      <c r="F27" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>3500</v>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J27" s="3">
         <v>3500</v>
       </c>
       <c r="K27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L27" s="3">
         <v>3200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>2300</v>
       </c>
       <c r="R27" s="3">
         <v>2300</v>
       </c>
       <c r="S27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T27" s="3">
         <v>2600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>2700</v>
       </c>
       <c r="U27" s="3">
         <v>2700</v>
       </c>
       <c r="V27" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W27" s="3">
         <v>1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,31 +2466,34 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-300</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
@@ -2432,123 +2502,129 @@
         <v>-200</v>
       </c>
       <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
         <v>6100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>5800</v>
       </c>
       <c r="O32" s="3">
         <v>5800</v>
       </c>
       <c r="P32" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Q32" s="3">
         <v>5200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4600</v>
-      </c>
-      <c r="W32" s="3">
-        <v>5200</v>
       </c>
       <c r="X32" s="3">
         <v>5200</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>5200</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>4100</v>
       </c>
-      <c r="F33" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>3500</v>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J33" s="3">
         <v>3500</v>
       </c>
       <c r="K33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L33" s="3">
         <v>3200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>2300</v>
       </c>
       <c r="R33" s="3">
         <v>2300</v>
       </c>
       <c r="S33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T33" s="3">
         <v>2600</v>
-      </c>
-      <c r="T33" s="3">
-        <v>2700</v>
       </c>
       <c r="U33" s="3">
         <v>2700</v>
       </c>
       <c r="V33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W33" s="3">
         <v>1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>4100</v>
       </c>
-      <c r="F35" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>3500</v>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J35" s="3">
         <v>3500</v>
       </c>
       <c r="K35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L35" s="3">
         <v>3200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>2300</v>
       </c>
       <c r="R35" s="3">
         <v>2300</v>
       </c>
       <c r="S35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T35" s="3">
         <v>2600</v>
-      </c>
-      <c r="T35" s="3">
-        <v>2700</v>
       </c>
       <c r="U35" s="3">
         <v>2700</v>
       </c>
       <c r="V35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W35" s="3">
         <v>1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45107</v>
       </c>
       <c r="L38" s="2">
         <v>45107</v>
       </c>
       <c r="M38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,82 +2916,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>19100</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3">
         <v>17200</v>
       </c>
-      <c r="F41" s="3">
-        <v>21600</v>
-      </c>
-      <c r="G41" s="3">
-        <v>15300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>18500</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>29700</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
-        <v>23900</v>
+      <c r="K41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L41" s="3">
         <v>23900</v>
       </c>
       <c r="M41" s="3">
+        <v>23900</v>
+      </c>
+      <c r="N41" s="3">
         <v>11100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7900</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2913,73 +3003,76 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>9100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>9500</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>200</v>
       </c>
       <c r="M42" s="3">
+        <v>200</v>
+      </c>
+      <c r="N42" s="3">
         <v>11900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>31100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>21200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>57400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>89400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>69600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>50900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>101900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>117200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>34100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>48000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>43500</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3010,8 +3103,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3052,8 +3145,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3084,8 +3180,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3126,40 +3222,43 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>32300</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
-        <v>30000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>37200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>32900</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
-        <v>32700</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>32700</v>
       </c>
       <c r="M45" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -3200,40 +3299,43 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>53000</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3">
         <v>27900</v>
       </c>
-      <c r="F46" s="3">
-        <v>54100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>54800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>51800</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>41000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
-        <v>58500</v>
+      <c r="K46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L46" s="3">
         <v>58500</v>
       </c>
       <c r="M46" s="3">
-        <v>0</v>
+        <v>58500</v>
       </c>
       <c r="N46" s="3">
         <v>0</v>
@@ -3274,40 +3376,43 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>164300</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>163100</v>
       </c>
-      <c r="F47" s="3">
-        <v>183100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>183600</v>
-      </c>
-      <c r="H47" s="3">
-        <v>185200</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>192600</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
-        <v>193400</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>193400</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
+        <v>193400</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3348,108 +3453,114 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>28200</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>27500</v>
       </c>
-      <c r="F48" s="3">
-        <v>27600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>27100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>27100</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>27400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
-        <v>27000</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>27000</v>
       </c>
       <c r="M48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="N48" s="3">
         <v>26800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>25400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>3500</v>
-      </c>
-      <c r="E49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3">
         <v>3700</v>
       </c>
-      <c r="F49" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3">
         <v>3700</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>3600</v>
@@ -3488,16 +3599,19 @@
         <v>3600</v>
       </c>
       <c r="X49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Y49" s="3">
         <v>1800</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,40 +3761,43 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>36600</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>55200</v>
       </c>
-      <c r="F52" s="3">
-        <v>33200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>31700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>34100</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>52700</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
-        <v>33300</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>33300</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,82 +3915,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>1771300</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3">
         <v>1692500</v>
       </c>
-      <c r="F54" s="3">
-        <v>1664800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1611900</v>
-      </c>
-      <c r="H54" s="3">
-        <v>1549600</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>1542800</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1424100</v>
+      <c r="K54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L54" s="3">
         <v>1424100</v>
       </c>
       <c r="M54" s="3">
+        <v>1424100</v>
+      </c>
+      <c r="N54" s="3">
         <v>1295400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1284700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1219000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1237900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1232800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1196700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1159300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1140400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1106600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1047000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1048400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>953200</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,114 +4052,118 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>1296200</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3">
         <v>1298100</v>
       </c>
-      <c r="F57" s="3">
-        <v>1296500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1270000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1192100</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>1179100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1091400</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L57" s="3">
         <v>1091400</v>
       </c>
       <c r="M57" s="3">
+        <v>1091400</v>
+      </c>
+      <c r="N57" s="3">
         <v>33600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>24600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>26900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>24700</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
         <v>209900</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>168000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>185600</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>194500</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
-        <v>169400</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>169400</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>169400</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4070,8 +4204,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4102,8 +4239,8 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -4144,40 +4281,43 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>1329500</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3">
         <v>1530200</v>
       </c>
-      <c r="F60" s="3">
-        <v>1327100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1477100</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1416300</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
         <v>1401000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1297300</v>
+      <c r="K60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L60" s="3">
         <v>1297300</v>
       </c>
       <c r="M60" s="3">
-        <v>0</v>
+        <v>1297300</v>
       </c>
       <c r="N60" s="3">
         <v>0</v>
@@ -4218,114 +4358,120 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>331800</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>53700</v>
       </c>
-      <c r="F61" s="3">
-        <v>233300</v>
-      </c>
       <c r="G61" s="3">
-        <v>35800</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>36500</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>47000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
-        <v>48100</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>48100</v>
       </c>
       <c r="M61" s="3">
+        <v>48100</v>
+      </c>
+      <c r="N61" s="3">
         <v>52400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>72900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>66800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>58900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>67200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>67800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>69500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>59100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>64700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>68000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>72500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>75300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>2500</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,82 +4743,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>1661300</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3">
         <v>1586400</v>
       </c>
-      <c r="F66" s="3">
-        <v>1560500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1512900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1452800</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>1450000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1345400</v>
+      <c r="K66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L66" s="3">
         <v>1345400</v>
       </c>
       <c r="M66" s="3">
+        <v>1345400</v>
+      </c>
+      <c r="N66" s="3">
         <v>1223500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1216700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1149200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1165400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1155700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1121000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1085200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1069200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1036600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>979600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>982800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>889500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,82 +5157,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>109400</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>107000</v>
       </c>
-      <c r="F72" s="3">
-        <v>104000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>100900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>98900</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>96900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
-        <v>91900</v>
+      <c r="K72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L72" s="3">
         <v>91900</v>
       </c>
       <c r="M72" s="3">
+        <v>91900</v>
+      </c>
+      <c r="N72" s="3">
         <v>85800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>83000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>80100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>76400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>74900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>73300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>71500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>69500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>67600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>66500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>65000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,82 +5465,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>110000</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3">
         <v>106100</v>
       </c>
-      <c r="F76" s="3">
-        <v>104300</v>
-      </c>
-      <c r="G76" s="3">
-        <v>99000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>96800</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3">
         <v>92800</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
-        <v>78700</v>
+      <c r="K76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L76" s="3">
         <v>78700</v>
       </c>
       <c r="M76" s="3">
+        <v>78700</v>
+      </c>
+      <c r="N76" s="3">
         <v>72000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>68000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>69800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>72400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>77100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>75700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>74100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>71100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>70000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>67300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>65700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>63700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45107</v>
       </c>
       <c r="L80" s="2">
         <v>45107</v>
       </c>
       <c r="M80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>4100</v>
       </c>
-      <c r="F81" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>3500</v>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J81" s="3">
         <v>3500</v>
       </c>
       <c r="K81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L81" s="3">
         <v>3200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>2300</v>
       </c>
       <c r="R81" s="3">
         <v>2300</v>
       </c>
       <c r="S81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T81" s="3">
         <v>2600</v>
-      </c>
-      <c r="T81" s="3">
-        <v>2700</v>
       </c>
       <c r="U81" s="3">
         <v>2700</v>
       </c>
       <c r="V81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W81" s="3">
         <v>1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5643,8 +5842,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5685,8 +5884,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,8 +6269,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6087,8 +6304,8 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -6129,8 +6346,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,8 +6377,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6189,8 +6410,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -6231,8 +6452,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,8 +6606,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6411,8 +6641,8 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -6453,8 +6683,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6513,8 +6747,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,8 +7020,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6809,8 +7055,8 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -6851,8 +7097,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6883,8 +7132,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6925,8 +7174,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6957,8 +7209,8 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -6997,6 +7249,9 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>
